--- a/nilai-oak/OAK_PAIK6203_2025_2_D.xlsx
+++ b/nilai-oak/OAK_PAIK6203_2025_2_D.xlsx
@@ -636,9 +636,15 @@
       </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
+      <c r="G8" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>37</v>
+      </c>
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="2">
         <f>ROUND( ((E8*10+F8*40+G8*10+H8*10+I8*15+J8*15) / 100), 2)</f>
@@ -683,9 +689,15 @@
       </c>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
+      <c r="G9" s="3" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2">
         <f>ROUND( ((E9*10+F9*40+G9*10+H9*10+I9*15+J9*15) / 100), 2)</f>
@@ -730,9 +742,15 @@
       </c>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
+      <c r="G10" s="3" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>17</v>
+      </c>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2">
         <f>ROUND( ((E10*10+F10*40+G10*10+H10*10+I10*15+J10*15) / 100), 2)</f>
@@ -777,9 +795,15 @@
       </c>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
+      <c r="G11" s="3" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>57</v>
+      </c>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="2">
         <f>ROUND( ((E11*10+F11*40+G11*10+H11*10+I11*15+J11*15) / 100), 2)</f>
@@ -824,9 +848,15 @@
       </c>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
+      <c r="G12" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>32</v>
+      </c>
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="2">
         <f>ROUND( ((E12*10+F12*40+G12*10+H12*10+I12*15+J12*15) / 100), 2)</f>
